--- a/plantillas/horario-consejeria-9C.xlsx
+++ b/plantillas/horario-consejeria-9C.xlsx
@@ -76,7 +76,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -89,11 +89,20 @@
         <color rgb="00DCE1E5"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="hair">
+        <color rgb="00DCE1E5"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -111,6 +120,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -493,11 +503,11 @@
           <t>HORARIO DE CLASES – 9°C</t>
         </is>
       </c>
-      <c r="B1" s="1" t="n"/>
-      <c r="C1" s="1" t="n"/>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="n"/>
+      <c r="B1" s="7" t="n"/>
+      <c r="C1" s="7" t="n"/>
+      <c r="D1" s="7" t="n"/>
+      <c r="E1" s="7" t="n"/>
+      <c r="F1" s="7" t="n"/>
     </row>
     <row r="2" ht="27" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -505,11 +515,11 @@
           <t>C.E.B.G. El Jiral · Consejería 2027</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
+      <c r="B2" s="7" t="n"/>
+      <c r="C2" s="7" t="n"/>
+      <c r="D2" s="7" t="n"/>
+      <c r="E2" s="7" t="n"/>
+      <c r="F2" s="7" t="n"/>
     </row>
     <row r="3" ht="27" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
@@ -546,7 +556,7 @@
     <row r="4" ht="27" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>12:20 – 12:55</t>
+          <t>Hora 1</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -578,7 +588,7 @@
     <row r="5" ht="27" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>12:55 – 13:30</t>
+          <t>Hora 2</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -610,7 +620,7 @@
     <row r="6" ht="27" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>13:30 – 14:05</t>
+          <t>Hora 3</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -642,7 +652,7 @@
     <row r="7" ht="27" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>14:05 – 14:40</t>
+          <t>Hora 4</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -677,16 +687,16 @@
           <t>☕ RECREO</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="7" t="n"/>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="7" t="n"/>
+      <c r="F8" s="7" t="n"/>
     </row>
     <row r="9" ht="27" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>15:00 – 15:35</t>
+          <t>Hora 5</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -718,7 +728,7 @@
     <row r="10" ht="27" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>15:35 – 16:10</t>
+          <t>Hora 6</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -750,7 +760,7 @@
     <row r="11" ht="27" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>16:10 – 16:45</t>
+          <t>Hora 7</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -782,7 +792,7 @@
     <row r="12" ht="27" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>16:45 – 17:20</t>
+          <t>Hora 8</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -896,7 +906,6 @@
           <t>Consejería</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -924,7 +933,6 @@
           <t>C. Naturales</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -952,7 +960,6 @@
           <t>C. Naturales</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -980,7 +987,6 @@
           <t>Matemáticas</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1008,7 +1014,6 @@
           <t>Orientación</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1036,7 +1041,6 @@
           <t>C. Naturales</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1064,7 +1068,6 @@
           <t>Inglés</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1092,7 +1095,6 @@
           <t>C. Naturales</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1120,7 +1122,6 @@
           <t>Contabilidad</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1148,7 +1149,6 @@
           <t>Educ. Física</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1176,7 +1176,6 @@
           <t>Geografía</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1204,7 +1203,6 @@
           <t>Agropecuaria</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1232,7 +1230,6 @@
           <t>Español</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1260,7 +1257,6 @@
           <t>F.D.C.</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1288,7 +1284,6 @@
           <t>Educ. Física</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1316,7 +1311,6 @@
           <t>Español</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1344,7 +1338,6 @@
           <t>Agropecuaria</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1372,7 +1365,6 @@
           <t>Español</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1400,7 +1392,6 @@
           <t>F.D.C.</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1428,7 +1419,6 @@
           <t>Español</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1456,7 +1446,6 @@
           <t>Inglés</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1484,7 +1473,6 @@
           <t>Español</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1512,7 +1500,6 @@
           <t>Matemáticas</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1540,7 +1527,6 @@
           <t>Geografía</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1568,7 +1554,6 @@
           <t>Religión</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1596,7 +1581,6 @@
           <t>Música</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1624,7 +1608,6 @@
           <t>Matemáticas</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1652,7 +1635,6 @@
           <t>Historia</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1680,7 +1662,6 @@
           <t>Inglés</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1708,7 +1689,6 @@
           <t>Contabilidad</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1736,7 +1716,6 @@
           <t>Historia</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1764,7 +1743,6 @@
           <t>Matemáticas</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1792,7 +1770,6 @@
           <t>Religión</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1820,7 +1797,6 @@
           <t>Exp. Artística</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1848,7 +1824,6 @@
           <t>Matemáticas</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1876,7 +1851,6 @@
           <t>Cívica</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1904,7 +1878,6 @@
           <t>Música</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1932,7 +1905,6 @@
           <t>Inglés</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1960,7 +1932,6 @@
           <t>Exp. Artística</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1988,7 +1959,6 @@
           <t>C. Naturales</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F41"/>
